--- a/docs/module_list.xlsx
+++ b/docs/module_list.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Placeholders/SM_Cube</t>
+          <t>/Game/Meshes/Placeholders/SM_Cube.SM_Cube</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
@@ -777,7 +777,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Residential_Block_Mid</t>
+          <t>/Game/Meshes/Modules/SM_Residential_Block_Mid.SM_Residential_Block_Mid</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
@@ -835,7 +835,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Residential_Terrace</t>
+          <t>/Game/Meshes/Modules/SM_Residential_Terrace.SM_Residential_Terrace</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
@@ -893,7 +893,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Placeholders/SM_Cube</t>
+          <t>/Game/Meshes/Placeholders/SM_Cube.SM_Cube</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Industrial_Processing</t>
+          <t>/Game/Meshes/Modules/SM_Industrial_Processing.SM_Industrial_Processing</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Placeholders/SM_Cube</t>
+          <t>/Game/Meshes/Placeholders/SM_Cube.SM_Cube</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Service_Utility_Block</t>
+          <t>/Game/Meshes/Modules/SM_Service_Utility_Block.SM_Service_Utility_Block</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Hull_Rib_Straight</t>
+          <t>/Game/Meshes/Modules/SM_Hull_Rib_Straight.SM_Hull_Rib_Straight</t>
         </is>
       </c>
       <c r="G9" s="6" t="n">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Hull_Rib_Junction</t>
+          <t>/Game/Meshes/Modules/SM_Hull_Rib_Junction.SM_Hull_Rib_Junction</t>
         </is>
       </c>
       <c r="G10" s="6" t="n">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_DeckPlate_Standard</t>
+          <t>/Game/Meshes/Modules/SM_DeckPlate_Standard.SM_DeckPlate_Standard</t>
         </is>
       </c>
       <c r="G11" s="6" t="n">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_DeckPlate_Corner</t>
+          <t>/Game/Meshes/Modules/SM_DeckPlate_Corner.SM_DeckPlate_Corner</t>
         </is>
       </c>
       <c r="G12" s="6" t="n">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Truss_LoadBearing</t>
+          <t>/Game/Meshes/Modules/SM_Truss_LoadBearing.SM_Truss_LoadBearing</t>
         </is>
       </c>
       <c r="G13" s="6" t="n">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Bulkhead_Segment</t>
+          <t>/Game/Meshes/Modules/SM_Bulkhead_Segment.SM_Bulkhead_Segment</t>
         </is>
       </c>
       <c r="G14" s="6" t="n">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Ground_Paved_Street</t>
+          <t>/Game/Meshes/Modules/SM_Ground_Paved_Street.SM_Ground_Paved_Street</t>
         </is>
       </c>
       <c r="G15" s="9" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Ground_Paved_Plaza</t>
+          <t>/Game/Meshes/Modules/SM_Ground_Paved_Plaza.SM_Ground_Paved_Plaza</t>
         </is>
       </c>
       <c r="G16" s="9" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Ground_Planted_Grass</t>
+          <t>/Game/Meshes/Modules/SM_Ground_Planted_Grass.SM_Ground_Planted_Grass</t>
         </is>
       </c>
       <c r="G17" s="9" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Ground_Transition</t>
+          <t>/Game/Meshes/Modules/SM_Ground_Transition.SM_Ground_Transition</t>
         </is>
       </c>
       <c r="G18" s="9" t="n">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Pathway_Straight</t>
+          <t>/Game/Meshes/Modules/SM_Pathway_Straight.SM_Pathway_Straight</t>
         </is>
       </c>
       <c r="G19" s="9" t="n">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Tree_Deciduous_Large</t>
+          <t>/Game/Meshes/Modules/SM_Tree_Deciduous_Large.SM_Tree_Deciduous_Large</t>
         </is>
       </c>
       <c r="G20" s="12" t="n">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Placeholders/SM_Cube</t>
+          <t>/Game/Meshes/Placeholders/SM_Cube.SM_Cube</t>
         </is>
       </c>
       <c r="G21" s="12" t="n">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Tree_Conifer</t>
+          <t>/Game/Meshes/Modules/SM_Tree_Conifer.SM_Tree_Conifer</t>
         </is>
       </c>
       <c r="G22" s="12" t="n">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Shrub_Cluster</t>
+          <t>/Game/Meshes/Modules/SM_Shrub_Cluster.SM_Shrub_Cluster</t>
         </is>
       </c>
       <c r="G23" s="12" t="n">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_GroundCover_Grass</t>
+          <t>/Game/Meshes/Modules/SM_GroundCover_Grass.SM_GroundCover_Grass</t>
         </is>
       </c>
       <c r="G24" s="12" t="n">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_GroundCover_Fern</t>
+          <t>/Game/Meshes/Modules/SM_GroundCover_Fern.SM_GroundCover_Fern</t>
         </is>
       </c>
       <c r="G25" s="12" t="n">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Crop_Row_Agricultural</t>
+          <t>/Game/Meshes/Modules/SM_Crop_Row_Agricultural.SM_Crop_Row_Agricultural</t>
         </is>
       </c>
       <c r="G26" s="12" t="n">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Planter_Box_Urban</t>
+          <t>/Game/Meshes/Modules/SM_Planter_Box_Urban.SM_Planter_Box_Urban</t>
         </is>
       </c>
       <c r="G27" s="12" t="n">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Pipe_Straight_Large</t>
+          <t>/Game/Meshes/Modules/SM_Pipe_Straight_Large.SM_Pipe_Straight_Large</t>
         </is>
       </c>
       <c r="G28" s="15" t="n">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Pipe_Elbow</t>
+          <t>/Game/Meshes/Modules/SM_Pipe_Elbow.SM_Pipe_Elbow</t>
         </is>
       </c>
       <c r="G29" s="15" t="n">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Vent_Wall_Mount</t>
+          <t>/Game/Meshes/Modules/SM_Vent_Wall_Mount.SM_Vent_Wall_Mount</t>
         </is>
       </c>
       <c r="G30" s="15" t="n">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_LightingRig_StreetLamp</t>
+          <t>/Game/Meshes/Modules/SM_LightingRig_StreetLamp.SM_LightingRig_StreetLamp</t>
         </is>
       </c>
       <c r="G31" s="15" t="n">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_LightingRig_OverheadStrip</t>
+          <t>/Game/Meshes/Modules/SM_LightingRig_OverheadStrip.SM_LightingRig_OverheadStrip</t>
         </is>
       </c>
       <c r="G32" s="15" t="n">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Cable_Conduit_Run</t>
+          <t>/Game/Meshes/Modules/SM_Cable_Conduit_Run.SM_Cable_Conduit_Run</t>
         </is>
       </c>
       <c r="G33" s="15" t="n">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_UtilityBox_Wall</t>
+          <t>/Game/Meshes/Modules/SM_UtilityBox_Wall.SM_UtilityBox_Wall</t>
         </is>
       </c>
       <c r="G34" s="15" t="n">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Decal_RustStreak</t>
+          <t>/Game/Meshes/Modules/SM_Decal_RustStreak.SM_Decal_RustStreak</t>
         </is>
       </c>
       <c r="G35" s="18" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Decal_Grime_Corner</t>
+          <t>/Game/Meshes/Modules/SM_Decal_Grime_Corner.SM_Decal_Grime_Corner</t>
         </is>
       </c>
       <c r="G36" s="18" t="n">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Clutter_CrateStack</t>
+          <t>/Game/Meshes/Modules/SM_Clutter_CrateStack.SM_Clutter_CrateStack</t>
         </is>
       </c>
       <c r="G37" s="18" t="n">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Mask_WeatheringOverlay</t>
+          <t>/Game/Meshes/Modules/SM_Mask_WeatheringOverlay.SM_Mask_WeatheringOverlay</t>
         </is>
       </c>
       <c r="G38" s="18" t="n">

--- a/docs/module_list.xlsx
+++ b/docs/module_list.xlsx
@@ -893,7 +893,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Placeholders/SM_Cube.SM_Cube</t>
+          <t>/Game/StarterContent/Shapes/Shape_Cylinder.Shape_Cylinder</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Placeholders/SM_Cube.SM_Cube</t>
+          <t>/Game/Meshes/Placeholders/SM_Cone.SM_Cone</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">

--- a/docs/module_list.xlsx
+++ b/docs/module_list.xlsx
@@ -777,7 +777,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Residential_Block_Mid.SM_Residential_Block_Mid</t>
+          <t>/Game/StarterContent/Shapes/Shape_Cube.Shape_Cube</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
@@ -835,7 +835,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Residential_Terrace.SM_Residential_Terrace</t>
+          <t>/Game/StarterContent/Shapes/Shape_Wedge_A.Shape_Wedge_A</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Industrial_Processing.SM_Industrial_Processing</t>
+          <t>/Game/StarterContent/Shapes/Shape_Tube.Shape_Tube</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>/Game/Meshes/Modules/SM_Service_Utility_Block.SM_Service_Utility_Block</t>
+          <t>/Game/StarterContent/Shapes/Shape_Sphere.Shape_Sphere</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
